--- a/templates/import/Шаблон_массового_импорта.xlsx
+++ b/templates/import/Шаблон_массового_импорта.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="R6ee6775b21fd434b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="2" r:id="R66636b6aebff46fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нормы" sheetId="3" r:id="R8bb4b354ac1a4c25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="4" r:id="R19cce1eaa4ca4961"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" r:id="Rdd173034b00b44e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="2" r:id="Rf7b451b9e56040b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нормы" sheetId="3" r:id="Re4b267265f9e4b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="4" r:id="Readb691fef2d465e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4240,7 +4240,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfecb2db7bd4d4266"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f3ab3369a0047ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31323,7 +31323,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d80322326614f80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb90b31f523e14daf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31333,7 +31333,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
@@ -31363,7 +31363,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="66" t="str">
-        <x:v>Торты базовые</x:v>
+        <x:v>Торты Базовые</x:v>
       </x:c>
       <x:c r="C2" s="66" t="str">
         <x:v>шт</x:v>
@@ -31381,7 +31381,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="66" t="str">
-        <x:v>Торты премиум</x:v>
+        <x:v>Торты Премиум</x:v>
       </x:c>
       <x:c r="C3" s="66"/>
       <x:c r="D3" s="66" t="str">
@@ -31397,7 +31397,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="66" t="str">
-        <x:v>Пироги и пирожные</x:v>
+        <x:v>Пироги</x:v>
       </x:c>
       <x:c r="C4" s="66"/>
       <x:c r="D4" s="66" t="str">
@@ -31411,7 +31411,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="66" t="str">
-        <x:v>Сухая выпечка</x:v>
+        <x:v>Десерты</x:v>
       </x:c>
       <x:c r="C5" s="66"/>
       <x:c r="D5" s="66" t="str">
@@ -31425,7 +31425,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="66" t="str">
-        <x:v>Прочее</x:v>
+        <x:v>Сухая выпечка</x:v>
       </x:c>
       <x:c r="C6" s="66"/>
       <x:c r="D6" s="66" t="str">
@@ -31438,7 +31438,9 @@
       <x:c r="A7" s="70" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="66"/>
+      <x:c r="B7" s="66" t="str">
+        <x:v>Прочее</x:v>
+      </x:c>
       <x:c r="C7" s="66"/>
       <x:c r="D7" s="66" t="str">
         <x:v>Суббота</x:v>
